--- a/data/trans_bre/P36BPD07_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P36BPD07_R-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,57</t>
+          <t>-3,48; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,61</t>
+          <t>0,9; 9,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,05</t>
+          <t>-3,84; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,12</t>
+          <t>1,16; 13,79</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,69%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,96</t>
+          <t>0,71; 6,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 7,09</t>
+          <t>0,56; 8,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,63</t>
+          <t>0,85; 8,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 10,64</t>
+          <t>0,84; 13,64</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,26</t>
+          <t>-4,19; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 18,32</t>
+          <t>-1,54; 7,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,31</t>
+          <t>-4,99; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 24,78</t>
+          <t>-1,96; 9,84</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,06</t>
+          <t>0,97; 7,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,56</t>
+          <t>2,49; 10,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,67</t>
+          <t>1,14; 8,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 18,03</t>
+          <t>3,45; 15,31</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,23</t>
+          <t>0,64; 3,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,2</t>
+          <t>2,74; 6,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,04</t>
+          <t>0,74; 4,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,73</t>
+          <t>3,77; 9,94</t>
         </is>
       </c>
     </row>
